--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488110_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488110_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5342</v>
+        <v>7.7865</v>
       </c>
       <c r="E2" t="n">
-        <v>5.39</v>
+        <v>5.2882</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1442</v>
+        <v>2.4984</v>
       </c>
       <c r="G2" t="n">
         <v>4.3314</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.401</v>
+        <v>0.6534</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0696</v>
+        <v>-0.1715</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4707</v>
+        <v>0.8249</v>
       </c>
       <c r="V2" t="n">
         <v>1.8107</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2532</v>
+        <v>4.6491</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6827</v>
+        <v>5.2752</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4295</v>
+        <v>-0.626</v>
       </c>
       <c r="G3" t="n">
         <v>4.6825</v>
@@ -688,13 +688,13 @@
         <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1831</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7453</v>
+        <v>0.3378</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4378</v>
+        <v>0.2412</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2071</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>O. ZARACHO PAEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9116</v>
+        <v>3.778</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1547</v>
+        <v>4.1646</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2432</v>
+        <v>-0.3866</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9484</v>
+        <v>1.979</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6806</v>
+        <v>1.3209</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2678</v>
+        <v>0.6581</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0635</v>
+        <v>2.9804</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1394</v>
+        <v>1.6546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9241</v>
+        <v>1.3259</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1151</v>
+        <v>-1.0014</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4588</v>
+        <v>-0.3337</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6563</v>
+        <v>-0.6677</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0425</v>
+        <v>-0.0028</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5581</v>
+        <v>-0.0229</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4844</v>
+        <v>0.0202</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. ZARACHO PAEZ</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.62</v>
+        <v>3.1838</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0627</v>
+        <v>3.7078</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4427</v>
+        <v>-0.524</v>
       </c>
       <c r="G5" t="n">
-        <v>1.979</v>
+        <v>0.9484</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3209</v>
+        <v>0.6806</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6581</v>
+        <v>0.2678</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9804</v>
+        <v>3.0635</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6546</v>
+        <v>2.1394</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3259</v>
+        <v>0.9241</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0014</v>
+        <v>-2.1151</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3337</v>
+        <v>-1.4588</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6677</v>
+        <v>-0.6563</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1608</v>
+        <v>0.3147</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1248</v>
+        <v>0.1112</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.036</v>
+        <v>0.2036</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2071</v>
+        <v>0.5331</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>0.5331</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8107</v>
+        <v>1.9972</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8107</v>
+        <v>2.2933</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.296</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8107</v>
+        <v>2.9636</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.4075</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2053</v>
+        <v>3.371</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8107</v>
+        <v>3.6758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.2214</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2053</v>
+        <v>3.8972</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.7123</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.1861</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.4332</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.1743</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.625</v>
+        <v>1.8107</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0895</v>
+        <v>1.8107</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4645</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9636</v>
+        <v>1.8107</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4075</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>3.371</v>
+        <v>1.2053</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6758</v>
+        <v>1.8107</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2214</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8972</v>
+        <v>1.2053</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7123</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1861</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8054</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8112</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0058</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3559</v>
+        <v>1.4889</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0622</v>
+        <v>1.5234</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2937</v>
+        <v>-0.0345</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3822</v>
+        <v>3.1474</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8549</v>
+        <v>2.0512</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5273</v>
+        <v>1.0962</v>
       </c>
       <c r="J8" t="n">
-        <v>5.8841</v>
+        <v>4.3253</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1079</v>
+        <v>2.8387</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7761</v>
+        <v>1.4866</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5019</v>
+        <v>-1.1779</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2531</v>
+        <v>-0.7875</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2488</v>
+        <v>-0.3904</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.7929</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.9822</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-3.9645</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.37</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1834</v>
+        <v>-0.4826</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1866</v>
+        <v>-0.046</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.674</v>
+        <v>-0.337</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.674</v>
+        <v>-0.337</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3413</v>
+        <v>1.4745</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3197</v>
+        <v>1.1246</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0216</v>
+        <v>0.3498</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1474</v>
+        <v>4.3822</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0512</v>
+        <v>1.8549</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0962</v>
+        <v>2.5273</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3253</v>
+        <v>5.8841</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8387</v>
+        <v>3.1079</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4866</v>
+        <v>2.7761</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1779</v>
+        <v>-1.5019</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7875</v>
+        <v>-1.2531</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3904</v>
+        <v>-0.2488</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6762</v>
+        <v>-0.2515</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6864</v>
+        <v>-0.121</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0101</v>
+        <v>-0.1305</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.337</v>
+        <v>-0.674</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.337</v>
+        <v>-0.674</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.432</v>
+        <v>1.3407</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1092</v>
+        <v>2.6809</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6771</v>
+        <v>-1.3402</v>
       </c>
       <c r="G10" t="n">
         <v>1.6574</v>
@@ -1234,13 +1234,13 @@
         <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6218</v>
+        <v>-0.7131</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8001</v>
+        <v>-0.2284</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8216</v>
+        <v>-0.4847</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1831</v>
+        <v>0.1954</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3411</v>
+        <v>2.6072</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5242</v>
+        <v>-2.4119</v>
       </c>
       <c r="G12" t="n">
         <v>0.8116</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4595</v>
+        <v>-1.0811</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9984</v>
+        <v>-0.7322</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4612</v>
+        <v>-0.3489</v>
       </c>
       <c r="V12" t="n">
         <v>0.2666</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3355</v>
+        <v>-1.3042</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4815</v>
+        <v>-1.7871</v>
       </c>
       <c r="F13" t="n">
-        <v>0.146</v>
+        <v>0.4829</v>
       </c>
       <c r="G13" t="n">
         <v>0.041</v>
@@ -1468,13 +1468,13 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5352</v>
+        <v>-0.5038</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0072</v>
+        <v>-0.3128</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5279</v>
+        <v>-0.191</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6254</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.0119</v>
+        <v>-3.7353</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.191</v>
+        <v>-3.0267</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8209</v>
+        <v>-0.7086</v>
       </c>
       <c r="G14" t="n">
         <v>-1.158</v>
@@ -1546,13 +1546,13 @@
         <v>0.7929</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4574</v>
+        <v>-0.1808</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.301</v>
+        <v>-0.1367</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1564</v>
+        <v>-0.0441</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>22.6561</v>
+        <v>22.968</v>
       </c>
       <c r="E15" t="n">
-        <v>25.65270000000001</v>
+        <v>25.9648</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9966</v>
+        <v>-2.9967</v>
       </c>
       <c r="G15" t="n">
         <v>25.8999</v>
@@ -1624,13 +1624,13 @@
         <v>15.8578</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.459699999999999</v>
+        <v>-2.1478</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.6787</v>
+        <v>-2.3665</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2190999999999997</v>
+        <v>0.2190000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-2.7662</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3639</v>
+        <v>-0.6561</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5861</v>
+        <v>2.0021</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2222</v>
+        <v>-2.6583</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.4204</v>
+        <v>-3.0965</v>
       </c>
       <c r="H17" t="n">
-        <v>1.784</v>
+        <v>-0.3071</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.2045</v>
+        <v>-2.7894</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5745</v>
+        <v>1.9084</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3708</v>
+        <v>1.2176</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.7963</v>
+        <v>0.6908</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.9949</v>
+        <v>-5.0049</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5867</v>
+        <v>-1.5247</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.4081</v>
+        <v>-3.4802</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5858</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5769</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9559</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1566</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>2.7993</v>
+        <v>0.4239</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4142</v>
+        <v>0.337</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6036</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>F. VALENCIA BARBOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6209</v>
+        <v>-0.7322</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2059</v>
+        <v>0.5493</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8267</v>
+        <v>-1.2816</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0965</v>
+        <v>-1.8725</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3071</v>
+        <v>0.5285</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.7894</v>
+        <v>-2.4011</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9084</v>
+        <v>0.4547</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2176</v>
+        <v>0.4508</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6908</v>
+        <v>0.0039</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.0049</v>
+        <v>-2.3272</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5247</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.4802</v>
+        <v>-2.405</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4158</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2975</v>
+        <v>0.0946</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2554</v>
+        <v>0.3211</v>
       </c>
       <c r="V18" t="n">
-        <v>0.337</v>
+        <v>-0.2666</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.337</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. VALENCIA BARBOSA</t>
+          <t>P. GUINDO CASTILLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7779</v>
+        <v>-1.1766</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4475</v>
+        <v>4.4771</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2254</v>
+        <v>-5.6537</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8725</v>
+        <v>-0.8109</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5285</v>
+        <v>-1.4537</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4011</v>
+        <v>0.6428</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4547</v>
+        <v>6.2688</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4508</v>
+        <v>0.6802</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0039</v>
+        <v>5.5886</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3272</v>
+        <v>-7.0797</v>
       </c>
       <c r="N19" t="n">
-        <v>0.07770000000000001</v>
+        <v>-2.134</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.405</v>
+        <v>-4.9457</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9911</v>
+        <v>-1.784</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.37</v>
+        <v>0.2112</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0072</v>
+        <v>0.1727</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3773</v>
+        <v>0.0384</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6285</v>
+        <v>-1.2563</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9969</v>
+        <v>-0.7931</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6317</v>
+        <v>-0.4632</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8987</v>
@@ -2014,13 +2014,13 @@
         <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.1505</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4992</v>
+        <v>-0.2954</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0235</v>
+        <v>0.145</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GUINDO CASTILLO</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7056</v>
+        <v>-1.7842</v>
       </c>
       <c r="E21" t="n">
-        <v>4.4771</v>
+        <v>0.5221</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.1826</v>
+        <v>-2.3063</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8109</v>
+        <v>-1.4976</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4537</v>
+        <v>1.9193</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6428</v>
+        <v>-3.4169</v>
       </c>
       <c r="J21" t="n">
-        <v>6.2688</v>
+        <v>0.6257</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6802</v>
+        <v>1.9036</v>
       </c>
       <c r="L21" t="n">
-        <v>5.5886</v>
+        <v>-1.2779</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.0797</v>
+        <v>-2.1233</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.134</v>
+        <v>0.0157</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.9457</v>
+        <v>-2.139</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3178</v>
+        <v>0.4625</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1727</v>
+        <v>0.0946</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4905</v>
+        <v>0.3679</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2071</v>
+        <v>-1.7403</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2184</v>
+        <v>-1.9053</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4202</v>
+        <v>0.6693</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6387</v>
+        <v>-2.5746</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4976</v>
+        <v>-4.4204</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9193</v>
+        <v>1.784</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.4169</v>
+        <v>-6.2045</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6257</v>
+        <v>1.5745</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9036</v>
+        <v>3.3708</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2779</v>
+        <v>-1.7963</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1233</v>
+        <v>-5.9949</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0157</v>
+        <v>-1.5867</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.139</v>
+        <v>-4.4081</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9911</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1982</v>
+        <v>-4.1627</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1893</v>
+        <v>2.5769</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0283</v>
+        <v>1.6867</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0072</v>
+        <v>0.2398</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0355</v>
+        <v>1.4469</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7403</v>
+        <v>2.4142</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7403</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0789</v>
+        <v>-5.0136</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.217</v>
+        <v>-1.6245</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8619</v>
+        <v>-3.3892</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1439</v>
@@ -2248,13 +2248,13 @@
         <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1771</v>
+        <v>0.2423</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4151</v>
+        <v>0.0076</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.238</v>
+        <v>0.2348</v>
       </c>
       <c r="V23" t="n">
         <v>0.2666</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>F. GARCIA GARRIDO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9139</v>
+        <v>-5.0934</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.035</v>
+        <v>-1.1851</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8789</v>
+        <v>-3.9083</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8936</v>
+        <v>-7.4762</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5428</v>
+        <v>-1.8706</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3507</v>
+        <v>-5.6057</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4912</v>
+        <v>-0.9341</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6117</v>
+        <v>0.2634</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1205</v>
+        <v>-1.1975</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4024</v>
+        <v>-6.5421</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9312</v>
+        <v>-2.134</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.4713</v>
+        <v>-4.4081</v>
       </c>
       <c r="P24" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-1.1893</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-1.9822</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4276</v>
+        <v>-0.1633</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5616</v>
+        <v>-0.2687</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1339</v>
+        <v>0.1054</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4033</v>
+        <v>1.9515</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4033</v>
+        <v>0.7444</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>F. GARCIA GARRIDO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2865</v>
+        <v>-5.5697</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1019</v>
+        <v>-2.8312</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.1846</v>
+        <v>-2.7385</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.4762</v>
+        <v>-2.8936</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8706</v>
+        <v>-1.5428</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.6057</v>
+        <v>-1.3507</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9341</v>
+        <v>-0.4912</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2634</v>
+        <v>-0.6117</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.1975</v>
+        <v>0.1205</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.5421</v>
+        <v>-2.4024</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.134</v>
+        <v>-0.9312</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.4081</v>
+        <v>-1.4713</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5947</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1893</v>
+        <v>-1.9822</v>
       </c>
       <c r="R25" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3564</v>
+        <v>-0.0835</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1855</v>
+        <v>-0.3578</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1708</v>
+        <v>0.2743</v>
       </c>
       <c r="V25" t="n">
-        <v>1.9515</v>
+        <v>-1.4033</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.7444</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-22.656</v>
+        <v>-21.9767</v>
       </c>
       <c r="E26" t="n">
-        <v>2.996700000000001</v>
+        <v>2.9967</v>
       </c>
       <c r="F26" t="n">
-        <v>-25.6527</v>
+        <v>-24.9737</v>
       </c>
       <c r="G26" t="n">
         <v>-25.8996</v>
@@ -2458,10 +2458,10 @@
         <v>13.1084</v>
       </c>
       <c r="K26" t="n">
-        <v>7.8748</v>
+        <v>7.874800000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>5.233599999999999</v>
+        <v>5.2336</v>
       </c>
       <c r="M26" t="n">
         <v>-39.008</v>
@@ -2482,13 +2482,13 @@
         <v>13.8756</v>
       </c>
       <c r="S26" t="n">
-        <v>2.459700000000001</v>
+        <v>3.1388</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2187999999999998</v>
+        <v>-0.2188</v>
       </c>
       <c r="U26" t="n">
-        <v>2.678600000000001</v>
+        <v>3.3577</v>
       </c>
       <c r="V26" t="n">
         <v>2.7662</v>
